--- a/slovakia-venture/models/Addendum_A_Model_LIVE.xlsx
+++ b/slovakia-venture/models/Addendum_A_Model_LIVE.xlsx
@@ -497,7 +497,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A36"/>
+  <dimension ref="A1:A40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="118" customWidth="1" min="1" max="1"/>
@@ -686,50 +686,78 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>5. DEPRECIATION IS CORRECTED. The source charges a flat 20,000 from 2028, i.e. 160,000/8 - but the</t>
+          <t>5. Funding_Portfolio: Regionalny prispevok is Include?=0 - its 05/10/2026 call lapsed. Excluding it</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t xml:space="preserve">   40,000 racking is not bought until 2029, so it depreciates an asset a year before purchase.</t>
+          <t xml:space="preserve">   moves P(at least one) from 99.99% to 99.98%, but removes a leg of the old cheapest trio.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Charged as incurred: 2028 = 15,000, 2029 onwards = 20,000. Effect: 2028 PBT is 19,280, not</t>
+          <t xml:space="preserve">   Do NOT replace it with SZRB + SIH NDF III: SZRB lends under the NDF III guarantee, so they are</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t xml:space="preserve">   14,280. Immaterial to any gate, but a live model should be right. Set the racking capex to 0</t>
+          <t xml:space="preserve">   one mechanism. Independent trio: microloan + LEO Feasibility + LEADER = 93.6%.</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   and the 2029 step disappears - which is the point of having inputs.</t>
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>6. DEPRECIATION IS CORRECTED. The source charges a flat 20,000 from 2028, i.e. 160,000/8 - but the</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" t="inlineStr"/>
+      <c r="A34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   40,000 racking is not bought until 2029, so it depreciates an asset a year before purchase.</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Tags: (F) fact from a source · (R) reasoned estimate · (O) opinion/assumption.</t>
+          <t xml:space="preserve">   Charged as incurred: 2028 = 15,000, 2029 onwards = 20,000. Effect: 2028 PBT is 19,280, not</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   14,280. Immaterial to any gate, but a live model should be right. Set the racking capex to 0</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   and the 2029 step disappears - which is the point of having inputs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Tags: (F) fact from a source · (R) reasoned estimate · (O) opinion/assumption.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
         <is>
           <t>Model numbers are (O) planning assumptions unless a source is cited.</t>
         </is>
@@ -2452,7 +2480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G23"/>
+  <dimension ref="A1:G26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -2616,7 +2644,7 @@
       </c>
       <c r="C8" s="7" t="inlineStr">
         <is>
-          <t>share of EUR13.9m; deadline 05/10/2026 (F)</t>
+          <t>LAPSED 05/10/2026; next call expected 2027 (F)</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
@@ -2628,7 +2656,7 @@
         <v>0.45</v>
       </c>
       <c r="F8" s="21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G8" s="20">
         <f>IF(F8=1,1-E8,1)</f>
@@ -2962,6 +2990,27 @@
     </row>
     <row r="23">
       <c r="B23" s="7" t="inlineStr">
+        <is>
+          <t>Regionalny prispevok is set to Include?=0: the 05/10/2026 call lapsed. Next call expected 2027.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" s="7" t="inlineStr">
+        <is>
+          <t>TRAP (F): SZRB lends UNDER the SIH NDF III guarantee - they are ONE mechanism, not two legs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" s="7" t="inlineStr">
+        <is>
+          <t>Independent trio clearing 90%: microloan 68% + LEO Feasibility 60% + LEADER 50% = 93.6%.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" s="7" t="inlineStr">
         <is>
           <t>Three applications to the same ministry are one application wearing three hats.</t>
         </is>
